--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -1873,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,6 +1912,16 @@
           <t>capacidad_diaria_tn</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>posiciones_consolidacion</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>contenedores_por_posicion_dia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1941,6 +1951,12 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1965,11 +1981,17 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1994,11 +2016,17 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2023,11 +2051,17 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2052,11 +2086,17 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2081,11 +2121,17 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2115,6 +2161,12 @@
       <c r="G8" t="n">
         <v>500</v>
       </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2143,6 +2195,12 @@
       </c>
       <c r="G9" t="n">
         <v>600</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3605,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3628,7 +3686,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3637,13 +3695,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3652,13 +3710,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3667,13 +3725,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3682,13 +3740,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3697,21 +3755,246 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>NORRY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BOREAS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BOREAS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BOREAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>16</v>
       </c>
     </row>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -1873,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,6 +1922,11 @@
           <t>contenedores_por_posicion_dia</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>posiciones_cross_dock</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1957,6 +1962,9 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1992,6 +2000,9 @@
       <c r="I3" t="n">
         <v>4</v>
       </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2027,6 +2038,9 @@
       <c r="I4" t="n">
         <v>4</v>
       </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2062,6 +2076,9 @@
       <c r="I5" t="n">
         <v>3</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2097,6 +2114,9 @@
       <c r="I6" t="n">
         <v>3</v>
       </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2132,6 +2152,9 @@
       <c r="I7" t="n">
         <v>3</v>
       </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2167,6 +2190,9 @@
       <c r="I8" t="n">
         <v>8</v>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2201,6 +2227,9 @@
       </c>
       <c r="I9" t="n">
         <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3663,7 +3692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,6 +3708,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>tipo_servicio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>tarifa_usd_tn</t>
         </is>
       </c>
@@ -3694,7 +3728,12 @@
           <t>JUGO</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3706,10 +3745,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3721,47 +3765,62 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>14</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JUGO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3769,14 +3828,19 @@
           <t>ACEITE</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>13</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3784,74 +3848,99 @@
           <t>JUGO</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>8</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>15</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JUGO</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>11</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>9</v>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3859,14 +3948,19 @@
           <t>ACEITE</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>12</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3874,74 +3968,99 @@
           <t>JUGO</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>9</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>14</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JUGO</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>10</v>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3949,14 +4068,19 @@
           <t>ACEITE</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>18</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3964,37 +4088,352 @@
           <t>JUGO</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>15</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CASCARA</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>11</v>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>16</v>
       </c>
     </row>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,51 @@
           <t>plazo_pedido_dias</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>camiones_producto</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>factor_produccion</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>factor_capacidad_planta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>factor_capacidad_deposito</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>factor_storage</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ventana_demanda</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>habilita_cross_dock</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>deterministico</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>estrategia_consolidacion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +538,710 @@
       </c>
       <c r="H2" t="n">
         <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>183</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
+        <v>400</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>183</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>400</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>183</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-04</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>183</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>400</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>183</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="n">
+        <v>400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E-06</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="n">
+        <v>400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E-07</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>183</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>183</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="n">
+        <v>400</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>183</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="n">
+        <v>400</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E-10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>183</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>400</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>183</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>400</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_TERMINAL</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,40 +473,60 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>camiones_portacontenedor</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>capacidad_camion_tn</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>velocidad_camion_kmh</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>horas_operativas_dia</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>factor_produccion</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>factor_capacidad_planta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>factor_capacidad_deposito</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>factor_storage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ventana_demanda</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>habilita_cross_dock</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>deterministico</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>estrategia_consolidacion</t>
         </is>
@@ -540,34 +560,46 @@
         <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -601,34 +633,46 @@
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -662,34 +706,46 @@
         <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -723,34 +779,46 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>70</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -784,34 +852,46 @@
         <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -845,34 +925,46 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -906,34 +998,46 @@
         <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -967,34 +1071,46 @@
         <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L9" t="n">
+        <v>70</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.7</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -1028,34 +1144,46 @@
         <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>70</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>0.5</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -1089,34 +1217,46 @@
         <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -1150,34 +1290,46 @@
         <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
@@ -1211,34 +1363,46 @@
         <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>CONSOLIDACION_TERMINAL</t>
         </is>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,16 @@
           <t>estrategia_consolidacion</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>cliente_default</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>calidad_default</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -604,6 +614,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,6 +697,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -750,6 +780,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -823,6 +863,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -896,6 +946,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -969,6 +1029,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1042,6 +1112,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1115,6 +1195,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1188,6 +1278,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1261,6 +1361,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1334,6 +1444,16 @@
           <t>CONSOLIDACION_DEPOSITO</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1405,6 +1525,16 @@
       <c r="U13" t="inlineStr">
         <is>
           <t>CONSOLIDACION_TERMINAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2729,6 +2859,11 @@
           <t>capacidad_contenedor_tn</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>toneladas_objetivo_lote_tn</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2744,6 +2879,9 @@
       <c r="C2" t="n">
         <v>25</v>
       </c>
+      <c r="D2" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2759,6 +2897,9 @@
       <c r="C3" t="n">
         <v>25</v>
       </c>
+      <c r="D3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2773,6 +2914,9 @@
       </c>
       <c r="C4" t="n">
         <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +541,31 @@
           <t>calidad_default</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>umbral_alerta_pct</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>umbral_sobrecarga_pct</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>umbral_objetivo_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>dias_forecast</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>politica_frio_propio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -624,6 +649,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X2" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -707,6 +749,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,6 +849,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -873,6 +949,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -956,6 +1049,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1039,6 +1149,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1122,6 +1249,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1205,6 +1349,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X9" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1288,6 +1449,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1371,6 +1549,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1454,6 +1649,23 @@
           <t>ESTANDAR</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1535,6 +1747,123 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>183</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="n">
+        <v>400</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>70</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>REACTIVA</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1941,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>237.507046379753</v>
+        <v>237.507046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1643,7 +1972,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>288.3300317983669</v>
+        <v>288.330032</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1674,7 +2003,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>406.4149548762916</v>
+        <v>406.414955</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1705,7 +2034,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>268.9640394587386</v>
+        <v>268.964039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1736,7 +2065,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>208.6183998755406</v>
+        <v>208.6184</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1767,7 +2096,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>264.0276511219731</v>
+        <v>264.027651</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1798,7 +2127,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>377.8306089584069</v>
+        <v>377.830609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1829,7 +2158,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>398.0240367223228</v>
+        <v>398.024037</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1860,7 +2189,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>232.1770813698146</v>
+        <v>232.177081</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1891,7 +2220,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>268.4655259315212</v>
+        <v>268.465526</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1922,7 +2251,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>435.0915240853604</v>
+        <v>435.091524</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1953,7 +2282,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>495.2241476027849</v>
+        <v>495.224148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1984,7 +2313,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>370.5324197464543</v>
+        <v>370.53242</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2015,7 +2344,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>468.6424595676131</v>
+        <v>468.64246</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2046,7 +2375,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>199.8188503304778</v>
+        <v>199.81885</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2077,7 +2406,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>257.7618215904504</v>
+        <v>257.761822</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2108,7 +2437,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>280.44283218421</v>
+        <v>280.442832</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2139,7 +2468,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>294.4426791769513</v>
+        <v>294.442679</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2170,7 +2499,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>283.5860107263849</v>
+        <v>283.586011</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2201,7 +2530,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>469.1931787026194</v>
+        <v>469.193179</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2232,7 +2561,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>30.16273366772705</v>
+        <v>30.162734</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2263,7 +2592,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>421.6623361446918</v>
+        <v>421.662336</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2294,7 +2623,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>299.7836698712717</v>
+        <v>299.78367</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2325,7 +2654,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>217.1313754365938</v>
+        <v>217.131375</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2356,7 +2685,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>393.8911845021509</v>
+        <v>393.891185</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2387,7 +2716,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>203.4269270602223</v>
+        <v>203.426927</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2418,7 +2747,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>456.0396813022595</v>
+        <v>456.039681</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2449,7 +2778,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>33.95891192716373</v>
+        <v>33.958912</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2480,7 +2809,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>483.0867187663691</v>
+        <v>483.086719</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2511,7 +2840,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>242.2561254851009</v>
+        <v>242.256125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2542,7 +2871,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>211.4135367820292</v>
+        <v>211.413537</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2573,7 +2902,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>223.831270262978</v>
+        <v>223.83127</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2604,7 +2933,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>424.635474842053</v>
+        <v>424.635475</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2635,7 +2964,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>384.7435180391079</v>
+        <v>384.743518</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2666,7 +2995,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>199.5352202831976</v>
+        <v>199.53522</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2697,7 +3026,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>242.60975422032</v>
+        <v>242.609754</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2728,7 +3057,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>209.4272891176739</v>
+        <v>209.427289</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2759,7 +3088,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>223.5014393452942</v>
+        <v>223.501439</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2790,7 +3119,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>257.3145990056882</v>
+        <v>257.314599</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2821,7 +3150,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>257.431638422302</v>
+        <v>257.431638</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2930,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,15 +3300,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>posiciones_consolidacion</t>
+          <t>contenedores_por_dia</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>contenedores_por_posicion_dia</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>posiciones_cross_dock</t>
         </is>
@@ -3019,9 +3343,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3052,12 +3373,9 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3090,12 +3408,9 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3128,12 +3443,9 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3166,12 +3478,9 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3204,12 +3513,9 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3242,12 +3548,9 @@
         <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3280,12 +3583,9 @@
         <v>600</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3857,7 +4157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,11 +4176,21 @@
           <t>storage_usd_tn_dia</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>oportunidad_usd_tn_dia</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>penalidad_sobrecarga_usd_tn_dia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3889,13 +4199,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3904,13 +4220,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3919,13 +4241,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.65</v>
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3934,13 +4262,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3949,13 +4283,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3964,13 +4304,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3979,13 +4325,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3994,13 +4346,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4009,13 +4367,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4024,13 +4388,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4039,13 +4409,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4054,13 +4430,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4069,13 +4451,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4084,22 +4472,97 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>DODERO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>0.68</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5545,7 +6008,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123.4237156028343</v>
+        <v>123.423716</v>
       </c>
     </row>
     <row r="3">
@@ -5563,7 +6026,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.52635653693826</v>
+        <v>54.526357</v>
       </c>
     </row>
     <row r="4">
@@ -5581,7 +6044,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.690526540466349</v>
+        <v>6.690527</v>
       </c>
     </row>
     <row r="5">
@@ -5599,7 +6062,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>90.63189795390065</v>
+        <v>90.63189800000001</v>
       </c>
     </row>
     <row r="6">
@@ -5617,7 +6080,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49.93545110769917</v>
+        <v>49.935451</v>
       </c>
     </row>
     <row r="7">
@@ -5635,7 +6098,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.010013865039539</v>
+        <v>6.010014</v>
       </c>
     </row>
     <row r="8">
@@ -5653,7 +6116,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71.76753433364162</v>
+        <v>71.767534</v>
       </c>
     </row>
     <row r="9">
@@ -5671,7 +6134,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60.53329944983113</v>
+        <v>60.533299</v>
       </c>
     </row>
     <row r="10">
@@ -5689,7 +6152,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.509906405603558</v>
+        <v>7.509906</v>
       </c>
     </row>
     <row r="11">
@@ -5707,7 +6170,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>104.3156425448662</v>
+        <v>104.315643</v>
       </c>
     </row>
     <row r="12">
@@ -5725,7 +6188,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.00709018303911</v>
+        <v>64.00709000000001</v>
       </c>
     </row>
     <row r="13">
@@ -5743,7 +6206,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.853025735123825</v>
+        <v>6.853026</v>
       </c>
     </row>
     <row r="14">
@@ -5761,7 +6224,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>94.97280195818007</v>
+        <v>94.972802</v>
       </c>
     </row>
     <row r="15">
@@ -5779,7 +6242,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>51.07874509122708</v>
+        <v>51.078745</v>
       </c>
     </row>
     <row r="16">
@@ -5797,7 +6260,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.733621138393808</v>
+        <v>8.733620999999999</v>
       </c>
     </row>
     <row r="17">
@@ -5815,7 +6278,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>114.3577754456944</v>
+        <v>114.357775</v>
       </c>
     </row>
     <row r="18">
@@ -5833,7 +6296,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58.29327805359124</v>
+        <v>58.293278</v>
       </c>
     </row>
     <row r="19">
@@ -5851,7 +6314,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.010636306118318</v>
+        <v>8.010636</v>
       </c>
     </row>
     <row r="20">
@@ -5869,7 +6332,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>106.3974992992745</v>
+        <v>106.397499</v>
       </c>
     </row>
     <row r="21">
@@ -5887,7 +6350,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54.36810215112272</v>
+        <v>54.368102</v>
       </c>
     </row>
     <row r="22">
@@ -5905,7 +6368,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.606957446775169</v>
+        <v>6.606957</v>
       </c>
     </row>
     <row r="23">
@@ -5923,7 +6386,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>142.4609848097078</v>
+        <v>142.460985</v>
       </c>
     </row>
     <row r="24">
@@ -5941,7 +6404,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63.19921550709721</v>
+        <v>63.199216</v>
       </c>
     </row>
     <row r="25">
@@ -5959,7 +6422,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6.367415546949093</v>
+        <v>6.367416</v>
       </c>
     </row>
     <row r="26">
@@ -5977,7 +6440,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>106.825438085891</v>
+        <v>106.825438</v>
       </c>
     </row>
     <row r="27">
@@ -5995,7 +6458,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49.53333774365814</v>
+        <v>49.533338</v>
       </c>
     </row>
     <row r="28">
@@ -6013,7 +6476,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.434079346966358</v>
+        <v>6.434079</v>
       </c>
     </row>
     <row r="29">
@@ -6031,7 +6494,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>102.4561092707146</v>
+        <v>102.456109</v>
       </c>
     </row>
     <row r="30">
@@ -6049,7 +6512,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>55.51988004433496</v>
+        <v>55.51988</v>
       </c>
     </row>
     <row r="31">
@@ -6067,7 +6530,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.400724021934243</v>
+        <v>6.400724</v>
       </c>
     </row>
     <row r="32">
@@ -6085,7 +6548,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>94.27901614856815</v>
+        <v>94.279016</v>
       </c>
     </row>
     <row r="33">
@@ -6103,7 +6566,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>46.52853653411862</v>
+        <v>46.528537</v>
       </c>
     </row>
     <row r="34">
@@ -6121,7 +6584,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.238928926210198</v>
+        <v>9.238929000000001</v>
       </c>
     </row>
     <row r="35">
@@ -6139,7 +6602,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>126.0135634183328</v>
+        <v>126.013563</v>
       </c>
     </row>
     <row r="36">
@@ -6157,7 +6620,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>52.53937739916856</v>
+        <v>52.539377</v>
       </c>
     </row>
     <row r="37">
@@ -6175,7 +6638,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.398978780799663</v>
+        <v>8.398979000000001</v>
       </c>
     </row>
     <row r="38">
@@ -6193,7 +6656,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>66.63717643799276</v>
+        <v>66.637176</v>
       </c>
     </row>
     <row r="39">
@@ -6211,7 +6674,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>54.14718932737922</v>
+        <v>54.147189</v>
       </c>
     </row>
     <row r="40">
@@ -6229,7 +6692,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.677893535060591</v>
+        <v>5.677894</v>
       </c>
     </row>
     <row r="41">
@@ -6247,7 +6710,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>90.09353750181404</v>
+        <v>90.093538</v>
       </c>
     </row>
     <row r="42">
@@ -6265,7 +6728,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60.00668168099415</v>
+        <v>60.006682</v>
       </c>
     </row>
     <row r="43">
@@ -6283,7 +6746,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.107491294088376</v>
+        <v>8.107491</v>
       </c>
     </row>
     <row r="44">
@@ -6301,7 +6764,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>103.5388850156264</v>
+        <v>103.538885</v>
       </c>
     </row>
     <row r="45">
@@ -6319,7 +6782,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>66.66909544283547</v>
+        <v>66.669095</v>
       </c>
     </row>
     <row r="46">
@@ -6337,7 +6800,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.11141709821054</v>
+        <v>11.111417</v>
       </c>
     </row>
     <row r="47">
@@ -6355,7 +6818,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>56.59406555210136</v>
+        <v>56.594066</v>
       </c>
     </row>
     <row r="48">
@@ -6373,7 +6836,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>54.08181119673985</v>
+        <v>54.081811</v>
       </c>
     </row>
     <row r="49">
@@ -6391,7 +6854,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5.873614148309532</v>
+        <v>5.873614</v>
       </c>
     </row>
     <row r="50">
@@ -6409,7 +6872,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>92.73392330600527</v>
+        <v>92.733923</v>
       </c>
     </row>
     <row r="51">
@@ -6427,7 +6890,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>55.08743694820427</v>
+        <v>55.087437</v>
       </c>
     </row>
     <row r="52">
@@ -6445,7 +6908,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.19522262955352</v>
+        <v>10.195223</v>
       </c>
     </row>
     <row r="53">
@@ -6463,7 +6926,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>131.0927443620271</v>
+        <v>131.092744</v>
       </c>
     </row>
     <row r="54">
@@ -6481,7 +6944,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>63.71085025499853</v>
+        <v>63.71085</v>
       </c>
     </row>
     <row r="55">
@@ -6499,7 +6962,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9.629384648601796</v>
+        <v>9.629384999999999</v>
       </c>
     </row>
     <row r="56">
@@ -6517,7 +6980,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>109.763725553759</v>
+        <v>109.763726</v>
       </c>
     </row>
     <row r="57">
@@ -6535,7 +6998,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>51.3052418919856</v>
+        <v>51.305242</v>
       </c>
     </row>
     <row r="58">
@@ -6553,7 +7016,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7.131083665838409</v>
+        <v>7.131084</v>
       </c>
     </row>
     <row r="59">
@@ -6571,7 +7034,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>112.3161656782536</v>
+        <v>112.316166</v>
       </c>
     </row>
     <row r="60">
@@ -6589,7 +7052,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>63.7858495860742</v>
+        <v>63.78585</v>
       </c>
     </row>
     <row r="61">
@@ -6607,7 +7070,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8.55913912192376</v>
+        <v>8.559139</v>
       </c>
     </row>
     <row r="62">
@@ -6625,7 +7088,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>84.34179834742368</v>
+        <v>84.341798</v>
       </c>
     </row>
     <row r="63">
@@ -6643,7 +7106,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>63.83434554851711</v>
+        <v>63.834346</v>
       </c>
     </row>
     <row r="64">
@@ -6661,7 +7124,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7.701177154289153</v>
+        <v>7.701177</v>
       </c>
     </row>
     <row r="65">
@@ -6679,7 +7142,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>104.8651915825623</v>
+        <v>104.865192</v>
       </c>
     </row>
     <row r="66">
@@ -6697,7 +7160,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>68.61517890115459</v>
+        <v>68.615179</v>
       </c>
     </row>
     <row r="67">
@@ -6715,7 +7178,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9.239275769092906</v>
+        <v>9.239276</v>
       </c>
     </row>
     <row r="68">
@@ -6733,7 +7196,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>100.0941543525679</v>
+        <v>100.094154</v>
       </c>
     </row>
     <row r="69">
@@ -6751,7 +7214,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>62.89875747648368</v>
+        <v>62.898757</v>
       </c>
     </row>
     <row r="70">
@@ -6769,7 +7232,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7.062112469824318</v>
+        <v>7.062112</v>
       </c>
     </row>
     <row r="71">
@@ -6787,7 +7250,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>107.1194416064023</v>
+        <v>107.119442</v>
       </c>
     </row>
     <row r="72">
@@ -6805,7 +7268,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>60.97360726125687</v>
+        <v>60.973607</v>
       </c>
     </row>
     <row r="73">
@@ -6823,7 +7286,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7.84921067782702</v>
+        <v>7.849211</v>
       </c>
     </row>
     <row r="74">
@@ -6841,7 +7304,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>135.586652158637</v>
+        <v>135.586652</v>
       </c>
     </row>
     <row r="75">
@@ -6859,7 +7322,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>56.68858280893279</v>
+        <v>56.688583</v>
       </c>
     </row>
     <row r="76">
@@ -6877,7 +7340,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7.018904465922895</v>
+        <v>7.018904</v>
       </c>
     </row>
     <row r="77">
@@ -6895,7 +7358,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>103.58936259091</v>
+        <v>103.589363</v>
       </c>
     </row>
     <row r="78">
@@ -6913,7 +7376,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>56.48997189853956</v>
+        <v>56.489972</v>
       </c>
     </row>
     <row r="79">
@@ -6931,7 +7394,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8.090688052086636</v>
+        <v>8.090688</v>
       </c>
     </row>
     <row r="80">
@@ -6949,7 +7412,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>114.275083608261</v>
+        <v>114.275084</v>
       </c>
     </row>
     <row r="81">
@@ -6967,7 +7430,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>49.52792510207032</v>
+        <v>49.527925</v>
       </c>
     </row>
     <row r="82">
@@ -6985,7 +7448,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8.384175897871311</v>
+        <v>8.384176</v>
       </c>
     </row>
     <row r="83">
@@ -7003,7 +7466,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>116.1471926462061</v>
+        <v>116.147193</v>
       </c>
     </row>
     <row r="84">
@@ -7021,7 +7484,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>44.7674689491374</v>
+        <v>44.767469</v>
       </c>
     </row>
     <row r="85">
@@ -7039,7 +7502,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>9.370416546713994</v>
+        <v>9.370417</v>
       </c>
     </row>
     <row r="86">
@@ -7057,7 +7520,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>94.36905566931961</v>
+        <v>94.369056</v>
       </c>
     </row>
     <row r="87">
@@ -7075,7 +7538,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>66.11734617471696</v>
+        <v>66.117346</v>
       </c>
     </row>
     <row r="88">
@@ -7093,7 +7556,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9.873141686034772</v>
+        <v>9.873142</v>
       </c>
     </row>
     <row r="89">
@@ -7111,7 +7574,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>92.64093145756014</v>
+        <v>92.64093099999999</v>
       </c>
     </row>
     <row r="90">
@@ -7129,7 +7592,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>53.05906231741933</v>
+        <v>53.059062</v>
       </c>
     </row>
     <row r="91">
@@ -7147,7 +7610,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6.295712610861935</v>
+        <v>6.295713</v>
       </c>
     </row>
     <row r="92">
@@ -7165,7 +7628,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>104.9810208838176</v>
+        <v>104.981021</v>
       </c>
     </row>
     <row r="93">
@@ -7183,7 +7646,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>65.02919444495834</v>
+        <v>65.029194</v>
       </c>
     </row>
     <row r="94">
@@ -7201,7 +7664,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7.294374847841277</v>
+        <v>7.294375</v>
       </c>
     </row>
     <row r="95">
@@ -7219,7 +7682,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>99.18233642179038</v>
+        <v>99.18233600000001</v>
       </c>
     </row>
     <row r="96">
@@ -7237,7 +7700,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>54.06017931750344</v>
+        <v>54.060179</v>
       </c>
     </row>
     <row r="97">
@@ -7255,7 +7718,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8.156046925218929</v>
+        <v>8.156046999999999</v>
       </c>
     </row>
     <row r="98">
@@ -7273,7 +7736,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>111.7756364517731</v>
+        <v>111.775636</v>
       </c>
     </row>
     <row r="99">
@@ -7291,7 +7754,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>77.01178552672762</v>
+        <v>77.011786</v>
       </c>
     </row>
     <row r="100">
@@ -7309,7 +7772,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8.414425553976862</v>
+        <v>8.414426000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7327,7 +7790,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>96.77548229461119</v>
+        <v>96.775482</v>
       </c>
     </row>
     <row r="102">
@@ -7345,7 +7808,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>50.89673864413027</v>
+        <v>50.896739</v>
       </c>
     </row>
     <row r="103">
@@ -7363,7 +7826,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8.998277737906117</v>
+        <v>8.998278000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7381,7 +7844,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>75.69080312567755</v>
+        <v>75.690803</v>
       </c>
     </row>
     <row r="105">
@@ -7399,7 +7862,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>69.64719426351022</v>
+        <v>69.647194</v>
       </c>
     </row>
     <row r="106">
@@ -7417,7 +7880,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7.049928829804862</v>
+        <v>7.049929</v>
       </c>
     </row>
     <row r="107">
@@ -7435,7 +7898,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>68.27722139361211</v>
+        <v>68.277221</v>
       </c>
     </row>
     <row r="108">
@@ -7453,7 +7916,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>58.68350844986146</v>
+        <v>58.683508</v>
       </c>
     </row>
     <row r="109">
@@ -7471,7 +7934,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6.433329946207406</v>
+        <v>6.43333</v>
       </c>
     </row>
     <row r="110">
@@ -7489,7 +7952,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>114.525520556725</v>
+        <v>114.525521</v>
       </c>
     </row>
     <row r="111">
@@ -7507,7 +7970,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>70.66743065320888</v>
+        <v>70.66743099999999</v>
       </c>
     </row>
     <row r="112">
@@ -7525,7 +7988,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8.137385933608719</v>
+        <v>8.137385999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7543,7 +8006,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>103.0279386390586</v>
+        <v>103.027939</v>
       </c>
     </row>
     <row r="114">
@@ -7561,7 +8024,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>69.90605909177259</v>
+        <v>69.906059</v>
       </c>
     </row>
     <row r="115">
@@ -7579,7 +8042,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.11597614372891</v>
+        <v>10.115976</v>
       </c>
     </row>
     <row r="116">
@@ -7597,7 +8060,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>94.62928224766324</v>
+        <v>94.629282</v>
       </c>
     </row>
     <row r="117">
@@ -7615,7 +8078,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>62.2718091096863</v>
+        <v>62.271809</v>
       </c>
     </row>
     <row r="118">
@@ -7633,7 +8096,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7.567772484905976</v>
+        <v>7.567772</v>
       </c>
     </row>
     <row r="119">
@@ -7651,7 +8114,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>110.6260068342574</v>
+        <v>110.626007</v>
       </c>
     </row>
     <row r="120">
@@ -7669,7 +8132,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>61.73021764117073</v>
+        <v>61.730218</v>
       </c>
     </row>
     <row r="121">
@@ -7687,7 +8150,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8.758764079613636</v>
+        <v>8.758763999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7705,7 +8168,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>88.90674733826475</v>
+        <v>88.906747</v>
       </c>
     </row>
     <row r="123">
@@ -7723,7 +8186,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>65.58804436084785</v>
+        <v>65.588044</v>
       </c>
     </row>
     <row r="124">
@@ -7741,7 +8204,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7.355637891618231</v>
+        <v>7.355638</v>
       </c>
     </row>
     <row r="125">
@@ -7759,7 +8222,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>119.0192487301824</v>
+        <v>119.019249</v>
       </c>
     </row>
     <row r="126">
@@ -7777,7 +8240,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>62.9720799873597</v>
+        <v>62.97208</v>
       </c>
     </row>
     <row r="127">
@@ -7795,7 +8258,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7.274086205910217</v>
+        <v>7.274086</v>
       </c>
     </row>
     <row r="128">
@@ -7813,7 +8276,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>81.43451847156827</v>
+        <v>81.434518</v>
       </c>
     </row>
     <row r="129">
@@ -7831,7 +8294,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>70.14938846192817</v>
+        <v>70.149388</v>
       </c>
     </row>
     <row r="130">
@@ -7849,7 +8312,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6.313188446133892</v>
+        <v>6.313188</v>
       </c>
     </row>
     <row r="131">
@@ -7867,7 +8330,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>71.49465085578211</v>
+        <v>71.494651</v>
       </c>
     </row>
     <row r="132">
@@ -7885,7 +8348,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>72.05205312637645</v>
+        <v>72.052053</v>
       </c>
     </row>
     <row r="133">
@@ -7903,7 +8366,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7.112059896276573</v>
+        <v>7.11206</v>
       </c>
     </row>
     <row r="134">
@@ -7921,7 +8384,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>116.7584408275423</v>
+        <v>116.758441</v>
       </c>
     </row>
     <row r="135">
@@ -7939,7 +8402,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>53.23966027727646</v>
+        <v>53.23966</v>
       </c>
     </row>
     <row r="136">
@@ -7957,7 +8420,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.13031703211017</v>
+        <v>10.130317</v>
       </c>
     </row>
     <row r="137">
@@ -7975,7 +8438,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>55.35440733452977</v>
+        <v>55.354407</v>
       </c>
     </row>
     <row r="138">
@@ -7993,7 +8456,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>55.19310785231043</v>
+        <v>55.193108</v>
       </c>
     </row>
     <row r="139">
@@ -8011,7 +8474,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.20997632470212</v>
+        <v>10.209976</v>
       </c>
     </row>
     <row r="140">
@@ -8029,7 +8492,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>110.9167987381884</v>
+        <v>110.916799</v>
       </c>
     </row>
     <row r="141">
@@ -8047,7 +8510,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>68.31035314027464</v>
+        <v>68.31035300000001</v>
       </c>
     </row>
     <row r="142">
@@ -8065,7 +8528,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7.145392060131186</v>
+        <v>7.145392</v>
       </c>
     </row>
     <row r="143">
@@ -8083,7 +8546,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>114.1840963780682</v>
+        <v>114.184096</v>
       </c>
     </row>
     <row r="144">
@@ -8101,7 +8564,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>46.03053546211622</v>
+        <v>46.030535</v>
       </c>
     </row>
     <row r="145">
@@ -8119,7 +8582,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7.608633033107829</v>
+        <v>7.608633</v>
       </c>
     </row>
     <row r="146">
@@ -8137,7 +8600,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>92.53707800624849</v>
+        <v>92.53707799999999</v>
       </c>
     </row>
     <row r="147">
@@ -8155,7 +8618,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>56.78466736286339</v>
+        <v>56.784667</v>
       </c>
     </row>
     <row r="148">
@@ -8173,7 +8636,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.2500790447072</v>
+        <v>10.250079</v>
       </c>
     </row>
     <row r="149">
@@ -8191,7 +8654,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>113.0157413574663</v>
+        <v>113.015741</v>
       </c>
     </row>
     <row r="150">
@@ -8209,7 +8672,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>63.22191645284617</v>
+        <v>63.221916</v>
       </c>
     </row>
     <row r="151">
@@ -8227,7 +8690,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6.083323136333495</v>
+        <v>6.083323</v>
       </c>
     </row>
     <row r="152">
@@ -8245,7 +8708,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>105.8567196447008</v>
+        <v>105.85672</v>
       </c>
     </row>
     <row r="153">
@@ -8263,7 +8726,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>61.87081618856955</v>
+        <v>61.870816</v>
       </c>
     </row>
     <row r="154">
@@ -8281,7 +8744,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>8.927755998377471</v>
+        <v>8.927756</v>
       </c>
     </row>
     <row r="155">
@@ -8299,7 +8762,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>89.20971781993697</v>
+        <v>89.209718</v>
       </c>
     </row>
     <row r="156">
@@ -8317,7 +8780,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>48.51844277536129</v>
+        <v>48.518443</v>
       </c>
     </row>
     <row r="157">
@@ -8335,7 +8798,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7.739395785864485</v>
+        <v>7.739396</v>
       </c>
     </row>
     <row r="158">
@@ -8353,7 +8816,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>117.4536327490732</v>
+        <v>117.453633</v>
       </c>
     </row>
     <row r="159">
@@ -8371,7 +8834,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>63.23717558170542</v>
+        <v>63.237176</v>
       </c>
     </row>
     <row r="160">
@@ -8389,7 +8852,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>9.180202463304871</v>
+        <v>9.180202</v>
       </c>
     </row>
     <row r="161">
@@ -8407,7 +8870,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>78.97138439145816</v>
+        <v>78.971384</v>
       </c>
     </row>
     <row r="162">
@@ -8425,7 +8888,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>53.19495819079611</v>
+        <v>53.194958</v>
       </c>
     </row>
     <row r="163">
@@ -8443,7 +8906,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6.947983988437873</v>
+        <v>6.947984</v>
       </c>
     </row>
     <row r="164">
@@ -8461,7 +8924,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>78.12407002439895</v>
+        <v>78.12407</v>
       </c>
     </row>
     <row r="165">
@@ -8479,7 +8942,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>51.42525421482171</v>
+        <v>51.425254</v>
       </c>
     </row>
     <row r="166">
@@ -8497,7 +8960,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>8.444868221641878</v>
+        <v>8.444868</v>
       </c>
     </row>
     <row r="167">
@@ -8515,7 +8978,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>104.7815098100012</v>
+        <v>104.78151</v>
       </c>
     </row>
     <row r="168">
@@ -8533,7 +8996,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>53.76170182717061</v>
+        <v>53.761702</v>
       </c>
     </row>
     <row r="169">
@@ -8551,7 +9014,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6.245165763501291</v>
+        <v>6.245166</v>
       </c>
     </row>
     <row r="170">
@@ -8569,7 +9032,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>98.00190557469162</v>
+        <v>98.00190600000001</v>
       </c>
     </row>
     <row r="171">
@@ -8587,7 +9050,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>60.43527882108253</v>
+        <v>60.435279</v>
       </c>
     </row>
     <row r="172">
@@ -8605,7 +9068,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7.164439139704093</v>
+        <v>7.164439</v>
       </c>
     </row>
     <row r="173">
@@ -8623,7 +9086,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>102.6781526281384</v>
+        <v>102.678153</v>
       </c>
     </row>
     <row r="174">
@@ -8641,7 +9104,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>68.66619932638682</v>
+        <v>68.66619900000001</v>
       </c>
     </row>
     <row r="175">
@@ -8659,7 +9122,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6.766413739882712</v>
+        <v>6.766414</v>
       </c>
     </row>
     <row r="176">
@@ -8677,7 +9140,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>89.50300197120391</v>
+        <v>89.503002</v>
       </c>
     </row>
     <row r="177">
@@ -8695,7 +9158,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>63.1346765063717</v>
+        <v>63.134677</v>
       </c>
     </row>
     <row r="178">
@@ -8713,7 +9176,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7.196993850608728</v>
+        <v>7.196994</v>
       </c>
     </row>
     <row r="179">
@@ -8731,7 +9194,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>81.92679066857909</v>
+        <v>81.92679099999999</v>
       </c>
     </row>
     <row r="180">
@@ -8749,7 +9212,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>49.47937769574568</v>
+        <v>49.479378</v>
       </c>
     </row>
     <row r="181">
@@ -8767,7 +9230,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>8.399349537264055</v>
+        <v>8.39935</v>
       </c>
     </row>
     <row r="182">
@@ -8785,7 +9248,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>120.7005894078328</v>
+        <v>120.700589</v>
       </c>
     </row>
     <row r="183">
@@ -8803,7 +9266,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>60.59835848617114</v>
+        <v>60.598358</v>
       </c>
     </row>
     <row r="184">
@@ -8821,7 +9284,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7.814652109856356</v>
+        <v>7.814652</v>
       </c>
     </row>
     <row r="185">
@@ -8839,7 +9302,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>93.14379348331164</v>
+        <v>93.143793</v>
       </c>
     </row>
     <row r="186">
@@ -8857,7 +9320,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>68.45821028180157</v>
+        <v>68.45820999999999</v>
       </c>
     </row>
     <row r="187">
@@ -8875,7 +9338,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>9.927847614176995</v>
+        <v>9.927847999999999</v>
       </c>
     </row>
     <row r="188">
@@ -8893,7 +9356,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>117.5657666784885</v>
+        <v>117.565767</v>
       </c>
     </row>
     <row r="189">
@@ -8911,7 +9374,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>43.60778662161306</v>
+        <v>43.607787</v>
       </c>
     </row>
     <row r="190">
@@ -8929,7 +9392,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>8.407012380045035</v>
+        <v>8.407012</v>
       </c>
     </row>
     <row r="191">
@@ -8947,7 +9410,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>102.1267071534905</v>
+        <v>102.126707</v>
       </c>
     </row>
     <row r="192">
@@ -8965,7 +9428,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>46.60188757879687</v>
+        <v>46.601888</v>
       </c>
     </row>
     <row r="193">
@@ -8983,7 +9446,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>7.640671710145654</v>
+        <v>7.640672</v>
       </c>
     </row>
     <row r="194">
@@ -9001,7 +9464,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>116.6428453779768</v>
+        <v>116.642845</v>
       </c>
     </row>
     <row r="195">
@@ -9019,7 +9482,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>48.43129285052934</v>
+        <v>48.431293</v>
       </c>
     </row>
     <row r="196">
@@ -9037,7 +9500,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>8.422034268823817</v>
+        <v>8.422034</v>
       </c>
     </row>
     <row r="197">
@@ -9055,7 +9518,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>94.2459104830458</v>
+        <v>94.24590999999999</v>
       </c>
     </row>
     <row r="198">
@@ -9073,7 +9536,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>55.52373811002104</v>
+        <v>55.523738</v>
       </c>
     </row>
     <row r="199">
@@ -9091,7 +9554,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>5.690681470395186</v>
+        <v>5.690681</v>
       </c>
     </row>
     <row r="200">
@@ -9109,7 +9572,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>140.768756671199</v>
+        <v>140.768757</v>
       </c>
     </row>
     <row r="201">
@@ -9127,7 +9590,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>70.95716188877711</v>
+        <v>70.957162</v>
       </c>
     </row>
     <row r="202">
@@ -9145,7 +9608,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6.706028656854308</v>
+        <v>6.706029</v>
       </c>
     </row>
     <row r="203">
@@ -9163,7 +9626,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>117.1754928679569</v>
+        <v>117.175493</v>
       </c>
     </row>
     <row r="204">
@@ -9181,7 +9644,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>58.87906416323742</v>
+        <v>58.879064</v>
       </c>
     </row>
     <row r="205">
@@ -9199,7 +9662,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>9.590178038072816</v>
+        <v>9.590178</v>
       </c>
     </row>
     <row r="206">
@@ -9217,7 +9680,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>103.5128056706869</v>
+        <v>103.512806</v>
       </c>
     </row>
     <row r="207">
@@ -9235,7 +9698,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>59.32597626731063</v>
+        <v>59.325976</v>
       </c>
     </row>
     <row r="208">
@@ -9253,7 +9716,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>8.125298562221513</v>
+        <v>8.125299</v>
       </c>
     </row>
     <row r="209">
@@ -9271,7 +9734,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>97.871240808536</v>
+        <v>97.871241</v>
       </c>
     </row>
     <row r="210">
@@ -9289,7 +9752,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>66.56515389778664</v>
+        <v>66.56515400000001</v>
       </c>
     </row>
     <row r="211">
@@ -9307,7 +9770,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>8.680264007335083</v>
+        <v>8.680263999999999</v>
       </c>
     </row>
     <row r="212">
@@ -9325,7 +9788,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>96.09339135274129</v>
+        <v>96.093391</v>
       </c>
     </row>
     <row r="213">
@@ -9343,7 +9806,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>52.34600514315758</v>
+        <v>52.346005</v>
       </c>
     </row>
     <row r="214">
@@ -9361,7 +9824,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>8.788269261409312</v>
+        <v>8.788269</v>
       </c>
     </row>
     <row r="215">
@@ -9379,7 +9842,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>89.2138053524608</v>
+        <v>89.21380499999999</v>
       </c>
     </row>
     <row r="216">
@@ -9397,7 +9860,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>71.92302884390962</v>
+        <v>71.923029</v>
       </c>
     </row>
     <row r="217">
@@ -9415,7 +9878,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>8.877691336118859</v>
+        <v>8.877691</v>
       </c>
     </row>
     <row r="218">
@@ -9433,7 +9896,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>92.97160891643894</v>
+        <v>92.971609</v>
       </c>
     </row>
     <row r="219">
@@ -9451,7 +9914,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>64.93540517240287</v>
+        <v>64.935405</v>
       </c>
     </row>
     <row r="220">
@@ -9469,7 +9932,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>6.425009056586881</v>
+        <v>6.425009</v>
       </c>
     </row>
     <row r="221">
@@ -9487,7 +9950,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>111.3288988836507</v>
+        <v>111.328899</v>
       </c>
     </row>
     <row r="222">
@@ -9505,7 +9968,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>65.72103993978581</v>
+        <v>65.72104</v>
       </c>
     </row>
     <row r="223">
@@ -9523,7 +9986,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>9.063324688931559</v>
+        <v>9.063325000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9541,7 +10004,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>98.4302102648991</v>
+        <v>98.43021</v>
       </c>
     </row>
     <row r="225">
@@ -9559,7 +10022,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>50.72303361779992</v>
+        <v>50.723034</v>
       </c>
     </row>
     <row r="226">
@@ -9577,7 +10040,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8.088689134375532</v>
+        <v>8.088689</v>
       </c>
     </row>
     <row r="227">
@@ -9595,7 +10058,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>125.4472890851421</v>
+        <v>125.447289</v>
       </c>
     </row>
     <row r="228">
@@ -9613,7 +10076,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>54.03799502056039</v>
+        <v>54.037995</v>
       </c>
     </row>
     <row r="229">
@@ -9631,7 +10094,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>8.107349370211397</v>
+        <v>8.107348999999999</v>
       </c>
     </row>
     <row r="230">
@@ -9649,7 +10112,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>95.48851163392725</v>
+        <v>95.488512</v>
       </c>
     </row>
     <row r="231">
@@ -9667,7 +10130,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>67.83819214079192</v>
+        <v>67.83819200000001</v>
       </c>
     </row>
     <row r="232">
@@ -9685,7 +10148,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>6.546341366214155</v>
+        <v>6.546341</v>
       </c>
     </row>
     <row r="233">
@@ -9703,7 +10166,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>109.528825487459</v>
+        <v>109.528825</v>
       </c>
     </row>
     <row r="234">
@@ -9721,7 +10184,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>56.89007917623123</v>
+        <v>56.890079</v>
       </c>
     </row>
     <row r="235">
@@ -9739,7 +10202,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>8.772164098887171</v>
+        <v>8.772164</v>
       </c>
     </row>
     <row r="236">
@@ -9757,7 +10220,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>106.0523115342147</v>
+        <v>106.052312</v>
       </c>
     </row>
     <row r="237">
@@ -9775,7 +10238,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>76.52671254204576</v>
+        <v>76.526713</v>
       </c>
     </row>
     <row r="238">
@@ -9793,7 +10256,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>6.717986366639371</v>
+        <v>6.717986</v>
       </c>
     </row>
     <row r="239">
@@ -9811,7 +10274,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>92.28102922770502</v>
+        <v>92.281029</v>
       </c>
     </row>
     <row r="240">
@@ -9829,7 +10292,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>68.36655440539994</v>
+        <v>68.36655399999999</v>
       </c>
     </row>
     <row r="241">
@@ -9847,7 +10310,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>8.781819131713888</v>
+        <v>8.781819</v>
       </c>
     </row>
     <row r="242">
@@ -9865,7 +10328,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>97.65834322373262</v>
+        <v>97.658343</v>
       </c>
     </row>
     <row r="243">
@@ -9883,7 +10346,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>72.56804053347312</v>
+        <v>72.56804099999999</v>
       </c>
     </row>
     <row r="244">
@@ -9901,7 +10364,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>6.98824950378648</v>
+        <v>6.98825</v>
       </c>
     </row>
     <row r="245">
@@ -9919,7 +10382,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>99.38282828841297</v>
+        <v>99.382828</v>
       </c>
     </row>
     <row r="246">
@@ -9937,7 +10400,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>34.72845140808155</v>
+        <v>34.728451</v>
       </c>
     </row>
     <row r="247">
@@ -9955,7 +10418,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6.638688111526723</v>
+        <v>6.638688</v>
       </c>
     </row>
     <row r="248">
@@ -9973,7 +10436,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>116.9923864477185</v>
+        <v>116.992386</v>
       </c>
     </row>
     <row r="249">
@@ -9991,7 +10454,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>54.87635134272264</v>
+        <v>54.876351</v>
       </c>
     </row>
     <row r="250">
@@ -10009,7 +10472,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>7.7687146139506</v>
+        <v>7.768715</v>
       </c>
     </row>
     <row r="251">
@@ -10027,7 +10490,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>84.27190762692179</v>
+        <v>84.271908</v>
       </c>
     </row>
     <row r="252">
@@ -10045,7 +10508,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>78.56756133637644</v>
+        <v>78.567561</v>
       </c>
     </row>
     <row r="253">
@@ -10063,7 +10526,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>8.25843825210978</v>
+        <v>8.258438</v>
       </c>
     </row>
     <row r="254">
@@ -10081,7 +10544,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>101.6179825788007</v>
+        <v>101.617983</v>
       </c>
     </row>
     <row r="255">
@@ -10099,7 +10562,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>67.43762608393133</v>
+        <v>67.43762599999999</v>
       </c>
     </row>
     <row r="256">
@@ -10117,7 +10580,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7.505538748815027</v>
+        <v>7.505539</v>
       </c>
     </row>
     <row r="257">
@@ -10135,7 +10598,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>83.08189822384043</v>
+        <v>83.081898</v>
       </c>
     </row>
     <row r="258">
@@ -10153,7 +10616,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>50.02365188060313</v>
+        <v>50.023652</v>
       </c>
     </row>
     <row r="259">
@@ -10171,7 +10634,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>7.921552331021571</v>
+        <v>7.921552</v>
       </c>
     </row>
     <row r="260">
@@ -10189,7 +10652,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>114.9086503963218</v>
+        <v>114.90865</v>
       </c>
     </row>
     <row r="261">
@@ -10207,7 +10670,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>57.91300233447823</v>
+        <v>57.913002</v>
       </c>
     </row>
     <row r="262">
@@ -10225,7 +10688,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>8.587716579411568</v>
+        <v>8.587717</v>
       </c>
     </row>
     <row r="263">
@@ -10243,7 +10706,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>133.4106622272184</v>
+        <v>133.410662</v>
       </c>
     </row>
     <row r="264">
@@ -10261,7 +10724,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>54.12484924260336</v>
+        <v>54.124849</v>
       </c>
     </row>
     <row r="265">
@@ -10279,7 +10742,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>7.413579422201879</v>
+        <v>7.413579</v>
       </c>
     </row>
     <row r="266">
@@ -10297,7 +10760,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>112.1659518460898</v>
+        <v>112.165952</v>
       </c>
     </row>
     <row r="267">
@@ -10315,7 +10778,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>46.31209747796293</v>
+        <v>46.312097</v>
       </c>
     </row>
     <row r="268">
@@ -10333,7 +10796,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>7.898424802013043</v>
+        <v>7.898425</v>
       </c>
     </row>
     <row r="269">
@@ -10351,7 +10814,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>100.8238621729976</v>
+        <v>100.823862</v>
       </c>
     </row>
     <row r="270">
@@ -10369,7 +10832,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>45.10246238411064</v>
+        <v>45.102462</v>
       </c>
     </row>
     <row r="271">
@@ -10387,7 +10850,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>9.456275196903604</v>
+        <v>9.456275</v>
       </c>
     </row>
     <row r="272">
@@ -10405,7 +10868,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>78.89072021180607</v>
+        <v>78.89072</v>
       </c>
     </row>
     <row r="273">
@@ -10423,7 +10886,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>72.56588997955657</v>
+        <v>72.56589</v>
       </c>
     </row>
     <row r="274">
@@ -10441,7 +10904,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>8.955766405649445</v>
+        <v>8.955766000000001</v>
       </c>
     </row>
     <row r="275">
@@ -10459,7 +10922,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>104.8936804027542</v>
+        <v>104.89368</v>
       </c>
     </row>
     <row r="276">
@@ -10477,7 +10940,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>61.73273353789417</v>
+        <v>61.732734</v>
       </c>
     </row>
     <row r="277">
@@ -10495,7 +10958,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>7.30308561667293</v>
+        <v>7.303086</v>
       </c>
     </row>
     <row r="278">
@@ -10513,7 +10976,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>132.4020873339294</v>
+        <v>132.402087</v>
       </c>
     </row>
     <row r="279">
@@ -10531,7 +10994,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>69.87889858852294</v>
+        <v>69.878899</v>
       </c>
     </row>
     <row r="280">
@@ -10549,7 +11012,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>8.076819459623266</v>
+        <v>8.076819</v>
       </c>
     </row>
     <row r="281">
@@ -10567,7 +11030,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>112.9888985943573</v>
+        <v>112.988899</v>
       </c>
     </row>
     <row r="282">
@@ -10585,7 +11048,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>56.73793094416013</v>
+        <v>56.737931</v>
       </c>
     </row>
     <row r="283">
@@ -10603,7 +11066,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>7.554625760048959</v>
+        <v>7.554626</v>
       </c>
     </row>
     <row r="284">
@@ -10621,7 +11084,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>108.575302861684</v>
+        <v>108.575303</v>
       </c>
     </row>
     <row r="285">
@@ -10639,7 +11102,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>66.9403291888475</v>
+        <v>66.94032900000001</v>
       </c>
     </row>
     <row r="286">
@@ -10657,7 +11120,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>10.58948064160063</v>
+        <v>10.589481</v>
       </c>
     </row>
     <row r="287">
@@ -10675,7 +11138,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>79.35950901072958</v>
+        <v>79.359509</v>
       </c>
     </row>
     <row r="288">
@@ -10693,7 +11156,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>38.31238911855613</v>
+        <v>38.312389</v>
       </c>
     </row>
     <row r="289">
@@ -10711,7 +11174,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>6.850300064175249</v>
+        <v>6.8503</v>
       </c>
     </row>
     <row r="290">
@@ -10729,7 +11192,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>116.5883528242555</v>
+        <v>116.588353</v>
       </c>
     </row>
     <row r="291">
@@ -10747,7 +11210,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>48.93935290209163</v>
+        <v>48.939353</v>
       </c>
     </row>
     <row r="292">
@@ -10765,7 +11228,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>8.69577384230452</v>
+        <v>8.695774</v>
       </c>
     </row>
     <row r="293">
@@ -10783,7 +11246,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>104.9656547192077</v>
+        <v>104.965655</v>
       </c>
     </row>
     <row r="294">
@@ -10801,7 +11264,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>76.12662561853314</v>
+        <v>76.126626</v>
       </c>
     </row>
     <row r="295">
@@ -10819,7 +11282,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>8.204829294763371</v>
+        <v>8.204829</v>
       </c>
     </row>
     <row r="296">
@@ -10837,7 +11300,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>106.8433413413232</v>
+        <v>106.843341</v>
       </c>
     </row>
     <row r="297">
@@ -10855,7 +11318,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>65.97029518584958</v>
+        <v>65.97029499999999</v>
       </c>
     </row>
     <row r="298">
@@ -10873,7 +11336,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>8.29411381363486</v>
+        <v>8.294114</v>
       </c>
     </row>
     <row r="299">
@@ -10891,7 +11354,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>74.16360652559518</v>
+        <v>74.163607</v>
       </c>
     </row>
     <row r="300">
@@ -10909,7 +11372,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>69.66650607168056</v>
+        <v>69.666506</v>
       </c>
     </row>
     <row r="301">
@@ -10927,7 +11390,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>9.013604443609768</v>
+        <v>9.013604000000001</v>
       </c>
     </row>
     <row r="302">
@@ -10945,7 +11408,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>88.76696949113845</v>
+        <v>88.766969</v>
       </c>
     </row>
     <row r="303">
@@ -10963,7 +11426,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>60.29674660083626</v>
+        <v>60.296747</v>
       </c>
     </row>
     <row r="304">
@@ -10981,7 +11444,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>9.636932311671192</v>
+        <v>9.636932</v>
       </c>
     </row>
     <row r="305">
@@ -10999,7 +11462,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>101.947358150045</v>
+        <v>101.947358</v>
       </c>
     </row>
     <row r="306">
@@ -11017,7 +11480,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>76.02674347525173</v>
+        <v>76.026743</v>
       </c>
     </row>
     <row r="307">
@@ -11035,7 +11498,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>8.279643353643632</v>
+        <v>8.279643</v>
       </c>
     </row>
     <row r="308">
@@ -11053,7 +11516,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>113.0538808147574</v>
+        <v>113.053881</v>
       </c>
     </row>
     <row r="309">
@@ -11071,7 +11534,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>72.87128064762075</v>
+        <v>72.871281</v>
       </c>
     </row>
     <row r="310">
@@ -11089,7 +11552,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>7.765575374030083</v>
+        <v>7.765575</v>
       </c>
     </row>
     <row r="311">
@@ -11107,7 +11570,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>108.8505732870849</v>
+        <v>108.850573</v>
       </c>
     </row>
     <row r="312">
@@ -11125,7 +11588,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>46.73044861324477</v>
+        <v>46.730449</v>
       </c>
     </row>
     <row r="313">
@@ -11143,7 +11606,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>7.209286256052712</v>
+        <v>7.209286</v>
       </c>
     </row>
     <row r="314">
@@ -11161,7 +11624,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>99.86216821317119</v>
+        <v>99.862168</v>
       </c>
     </row>
     <row r="315">
@@ -11179,7 +11642,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>64.48515690545314</v>
+        <v>64.485157</v>
       </c>
     </row>
     <row r="316">
@@ -11197,7 +11660,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>8.875940275099683</v>
+        <v>8.87594</v>
       </c>
     </row>
     <row r="317">
@@ -11215,7 +11678,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>116.6319586469394</v>
+        <v>116.631959</v>
       </c>
     </row>
     <row r="318">
@@ -11233,7 +11696,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>52.07795257227097</v>
+        <v>52.077953</v>
       </c>
     </row>
     <row r="319">
@@ -11251,7 +11714,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>7.789614656557659</v>
+        <v>7.789615</v>
       </c>
     </row>
     <row r="320">
@@ -11269,7 +11732,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>106.3678609690536</v>
+        <v>106.367861</v>
       </c>
     </row>
     <row r="321">
@@ -11287,7 +11750,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>62.79726805402673</v>
+        <v>62.797268</v>
       </c>
     </row>
     <row r="322">
@@ -11305,7 +11768,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>8.006999151331462</v>
+        <v>8.006999</v>
       </c>
     </row>
     <row r="323">
@@ -11323,7 +11786,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>69.16428524862603</v>
+        <v>69.16428500000001</v>
       </c>
     </row>
     <row r="324">
@@ -11341,7 +11804,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>56.77623934985311</v>
+        <v>56.776239</v>
       </c>
     </row>
     <row r="325">
@@ -11359,7 +11822,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>6.869885646229445</v>
+        <v>6.869886</v>
       </c>
     </row>
     <row r="326">
@@ -11377,7 +11840,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>76.36747116154146</v>
+        <v>76.36747099999999</v>
       </c>
     </row>
     <row r="327">
@@ -11395,7 +11858,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>67.94206881350293</v>
+        <v>67.942069</v>
       </c>
     </row>
     <row r="328">
@@ -11413,7 +11876,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>6.0840070438309</v>
+        <v>6.084007</v>
       </c>
     </row>
     <row r="329">
@@ -11431,7 +11894,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>97.4350422771428</v>
+        <v>97.435042</v>
       </c>
     </row>
     <row r="330">
@@ -11449,7 +11912,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>52.57551014000843</v>
+        <v>52.57551</v>
       </c>
     </row>
     <row r="331">
@@ -11467,7 +11930,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>8.092050847746783</v>
+        <v>8.092051</v>
       </c>
     </row>
     <row r="332">
@@ -11485,7 +11948,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>105.3989108186991</v>
+        <v>105.398911</v>
       </c>
     </row>
     <row r="333">
@@ -11503,7 +11966,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>63.71523912399226</v>
+        <v>63.715239</v>
       </c>
     </row>
     <row r="334">
@@ -11521,7 +11984,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>6.952361070476504</v>
+        <v>6.952361</v>
       </c>
     </row>
     <row r="335">
@@ -11539,7 +12002,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>102.1011513621211</v>
+        <v>102.101151</v>
       </c>
     </row>
     <row r="336">
@@ -11557,7 +12020,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>41.08174338758826</v>
+        <v>41.081743</v>
       </c>
     </row>
     <row r="337">
@@ -11575,7 +12038,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>7.681223605750469</v>
+        <v>7.681224</v>
       </c>
     </row>
     <row r="338">
@@ -11593,7 +12056,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>117.1065377515377</v>
+        <v>117.106538</v>
       </c>
     </row>
     <row r="339">
@@ -11611,7 +12074,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>60.56115744276636</v>
+        <v>60.561157</v>
       </c>
     </row>
     <row r="340">
@@ -11629,7 +12092,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>7.120854356628134</v>
+        <v>7.120854</v>
       </c>
     </row>
     <row r="341">
@@ -11647,7 +12110,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>113.7722535406835</v>
+        <v>113.772254</v>
       </c>
     </row>
     <row r="342">
@@ -11665,7 +12128,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>48.43413032029427</v>
+        <v>48.43413</v>
       </c>
     </row>
     <row r="343">
@@ -11683,7 +12146,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>8.467196131812624</v>
+        <v>8.467196</v>
       </c>
     </row>
     <row r="344">
@@ -11701,7 +12164,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>83.33432885131609</v>
+        <v>83.334329</v>
       </c>
     </row>
     <row r="345">
@@ -11719,7 +12182,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>63.31677259999384</v>
+        <v>63.316773</v>
       </c>
     </row>
     <row r="346">
@@ -11737,7 +12200,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>7.967778547749804</v>
+        <v>7.967779</v>
       </c>
     </row>
     <row r="347">
@@ -11755,7 +12218,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>112.7820273598555</v>
+        <v>112.782027</v>
       </c>
     </row>
     <row r="348">
@@ -11773,7 +12236,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>58.50989611558339</v>
+        <v>58.509896</v>
       </c>
     </row>
     <row r="349">
@@ -11791,7 +12254,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9.877847858064666</v>
+        <v>9.877848</v>
       </c>
     </row>
     <row r="350">
@@ -11809,7 +12272,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>119.9064975314208</v>
+        <v>119.906498</v>
       </c>
     </row>
     <row r="351">
@@ -11827,7 +12290,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>60.59653721488959</v>
+        <v>60.596537</v>
       </c>
     </row>
     <row r="352">
@@ -11845,7 +12308,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>6.623886795339565</v>
+        <v>6.623887</v>
       </c>
     </row>
     <row r="353">
@@ -11863,7 +12326,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>97.25492962010904</v>
+        <v>97.25493</v>
       </c>
     </row>
     <row r="354">
@@ -11881,7 +12344,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>67.3936311743814</v>
+        <v>67.393631</v>
       </c>
     </row>
     <row r="355">
@@ -11899,7 +12362,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>8.288214332252752</v>
+        <v>8.288214</v>
       </c>
     </row>
     <row r="356">
@@ -11917,7 +12380,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>99.58470085667103</v>
+        <v>99.584701</v>
       </c>
     </row>
     <row r="357">
@@ -11935,7 +12398,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>70.70762266075172</v>
+        <v>70.707623</v>
       </c>
     </row>
     <row r="358">
@@ -11953,7 +12416,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>6.315938188118204</v>
+        <v>6.315938</v>
       </c>
     </row>
     <row r="359">
@@ -11971,7 +12434,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>98.30415688040445</v>
+        <v>98.304157</v>
       </c>
     </row>
     <row r="360">
@@ -11989,7 +12452,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>65.0907321631706</v>
+        <v>65.090732</v>
       </c>
     </row>
     <row r="361">
@@ -12007,7 +12470,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>5.978971048085242</v>
+        <v>5.978971</v>
       </c>
     </row>
     <row r="362">
@@ -12025,7 +12488,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>94.70606942933006</v>
+        <v>94.706069</v>
       </c>
     </row>
     <row r="363">
@@ -12043,7 +12506,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>47.4857654296666</v>
+        <v>47.485765</v>
       </c>
     </row>
     <row r="364">
@@ -12061,7 +12524,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>9.350853208109889</v>
+        <v>9.350853000000001</v>
       </c>
     </row>
     <row r="365">
@@ -12079,7 +12542,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>112.4091575296108</v>
+        <v>112.409158</v>
       </c>
     </row>
     <row r="366">
@@ -12097,7 +12560,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>58.4321353017955</v>
+        <v>58.432135</v>
       </c>
     </row>
     <row r="367">
@@ -12115,7 +12578,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>7.759315594101511</v>
+        <v>7.759316</v>
       </c>
     </row>
     <row r="368">
@@ -12133,7 +12596,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>108.565523734929</v>
+        <v>108.565524</v>
       </c>
     </row>
     <row r="369">
@@ -12151,7 +12614,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>52.63447311066277</v>
+        <v>52.634473</v>
       </c>
     </row>
     <row r="370">
@@ -12169,7 +12632,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>7.377728524539212</v>
+        <v>7.377729</v>
       </c>
     </row>
     <row r="371">
@@ -12187,7 +12650,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>115.075408056558</v>
+        <v>115.075408</v>
       </c>
     </row>
     <row r="372">
@@ -12205,7 +12668,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>52.7838750859428</v>
+        <v>52.783875</v>
       </c>
     </row>
     <row r="373">
@@ -12223,7 +12686,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>7.247326010803778</v>
+        <v>7.247326</v>
       </c>
     </row>
     <row r="374">
@@ -12241,7 +12704,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>91.9670333022496</v>
+        <v>91.967033</v>
       </c>
     </row>
     <row r="375">
@@ -12259,7 +12722,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>58.27414250498227</v>
+        <v>58.274143</v>
       </c>
     </row>
     <row r="376">
@@ -12277,7 +12740,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>8.772642783323141</v>
+        <v>8.772643</v>
       </c>
     </row>
     <row r="377">
@@ -12295,7 +12758,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>88.96382726737167</v>
+        <v>88.96382699999999</v>
       </c>
     </row>
     <row r="378">
@@ -12313,7 +12776,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>46.63747170263169</v>
+        <v>46.637472</v>
       </c>
     </row>
     <row r="379">
@@ -12331,7 +12794,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>5.387042780072139</v>
+        <v>5.387043</v>
       </c>
     </row>
     <row r="380">
@@ -12349,7 +12812,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>102.7438431962479</v>
+        <v>102.743843</v>
       </c>
     </row>
     <row r="381">
@@ -12367,7 +12830,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>77.06071505776511</v>
+        <v>77.060715</v>
       </c>
     </row>
     <row r="382">
@@ -12385,7 +12848,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>7.769297591334825</v>
+        <v>7.769298</v>
       </c>
     </row>
     <row r="383">
@@ -12403,7 +12866,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>100.8416468862733</v>
+        <v>100.841647</v>
       </c>
     </row>
     <row r="384">
@@ -12421,7 +12884,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>49.41754988473487</v>
+        <v>49.41755</v>
       </c>
     </row>
     <row r="385">
@@ -12439,7 +12902,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>5.601619331611801</v>
+        <v>5.601619</v>
       </c>
     </row>
     <row r="386">
@@ -12457,7 +12920,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>104.1203539318037</v>
+        <v>104.120354</v>
       </c>
     </row>
     <row r="387">
@@ -12475,7 +12938,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>71.54747829797344</v>
+        <v>71.547478</v>
       </c>
     </row>
     <row r="388">
@@ -12493,7 +12956,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>8.689485079310337</v>
+        <v>8.689484999999999</v>
       </c>
     </row>
     <row r="389">
@@ -12511,7 +12974,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>107.8441381089179</v>
+        <v>107.844138</v>
       </c>
     </row>
     <row r="390">
@@ -12529,7 +12992,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>64.18714968242732</v>
+        <v>64.18715</v>
       </c>
     </row>
     <row r="391">
@@ -12547,7 +13010,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>9.567227055455255</v>
+        <v>9.567227000000001</v>
       </c>
     </row>
     <row r="392">
@@ -12565,7 +13028,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>99.17850146987139</v>
+        <v>99.178501</v>
       </c>
     </row>
     <row r="393">
@@ -12583,7 +13046,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>53.79549246804864</v>
+        <v>53.795492</v>
       </c>
     </row>
     <row r="394">
@@ -12601,7 +13064,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>8.93898646292147</v>
+        <v>8.938986</v>
       </c>
     </row>
     <row r="395">
@@ -12619,7 +13082,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>110.8448910857584</v>
+        <v>110.844891</v>
       </c>
     </row>
     <row r="396">
@@ -12637,7 +13100,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>64.06103568121063</v>
+        <v>64.061036</v>
       </c>
     </row>
     <row r="397">
@@ -12655,7 +13118,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>6.785314928404546</v>
+        <v>6.785315</v>
       </c>
     </row>
     <row r="398">
@@ -12673,7 +13136,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>92.15081119452448</v>
+        <v>92.150811</v>
       </c>
     </row>
     <row r="399">
@@ -12691,7 +13154,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>61.9848897373773</v>
+        <v>61.98489</v>
       </c>
     </row>
     <row r="400">
@@ -12709,7 +13172,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>6.848213692231539</v>
+        <v>6.848214</v>
       </c>
     </row>
     <row r="401">
@@ -12727,7 +13190,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>111.1147176602071</v>
+        <v>111.114718</v>
       </c>
     </row>
     <row r="402">
@@ -12745,7 +13208,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>50.22040548376101</v>
+        <v>50.220405</v>
       </c>
     </row>
     <row r="403">
@@ -12763,7 +13226,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>8.183218647907756</v>
+        <v>8.183218999999999</v>
       </c>
     </row>
     <row r="404">
@@ -12781,7 +13244,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>98.30353127595933</v>
+        <v>98.30353100000001</v>
       </c>
     </row>
     <row r="405">
@@ -12799,7 +13262,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>74.00391306673703</v>
+        <v>74.003913</v>
       </c>
     </row>
     <row r="406">
@@ -12817,7 +13280,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>7.807415209942618</v>
+        <v>7.807415</v>
       </c>
     </row>
     <row r="407">
@@ -12835,7 +13298,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>105.753294858258</v>
+        <v>105.753295</v>
       </c>
     </row>
     <row r="408">
@@ -12853,7 +13316,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>67.36695575982198</v>
+        <v>67.366956</v>
       </c>
     </row>
     <row r="409">
@@ -12871,7 +13334,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>8.492332841437854</v>
+        <v>8.492333</v>
       </c>
     </row>
     <row r="410">
@@ -12889,7 +13352,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>94.13495077937634</v>
+        <v>94.134951</v>
       </c>
     </row>
     <row r="411">
@@ -12907,7 +13370,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>60.68962864001989</v>
+        <v>60.689629</v>
       </c>
     </row>
     <row r="412">
@@ -12925,7 +13388,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>9.10626907925089</v>
+        <v>9.106268999999999</v>
       </c>
     </row>
     <row r="413">
@@ -12943,7 +13406,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>102.5566529036563</v>
+        <v>102.556653</v>
       </c>
     </row>
     <row r="414">
@@ -12961,7 +13424,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>60.2030922014013</v>
+        <v>60.203092</v>
       </c>
     </row>
     <row r="415">
@@ -12979,7 +13442,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>6.299077056425199</v>
+        <v>6.299077</v>
       </c>
     </row>
     <row r="416">
@@ -12997,7 +13460,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>74.25038253019667</v>
+        <v>74.250383</v>
       </c>
     </row>
     <row r="417">
@@ -13015,7 +13478,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>53.36881261512696</v>
+        <v>53.368813</v>
       </c>
     </row>
     <row r="418">
@@ -13033,7 +13496,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>8.545554913639089</v>
+        <v>8.545555</v>
       </c>
     </row>
     <row r="419">
@@ -13051,7 +13514,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>96.1086601240778</v>
+        <v>96.10866</v>
       </c>
     </row>
     <row r="420">
@@ -13069,7 +13532,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>40.98157679876417</v>
+        <v>40.981577</v>
       </c>
     </row>
     <row r="421">
@@ -13087,7 +13550,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>7.77801859133654</v>
+        <v>7.778019</v>
       </c>
     </row>
     <row r="422">
@@ -13105,7 +13568,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>119.9776964990004</v>
+        <v>119.977696</v>
       </c>
     </row>
     <row r="423">
@@ -13123,7 +13586,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>54.56568836501788</v>
+        <v>54.565688</v>
       </c>
     </row>
     <row r="424">
@@ -13141,7 +13604,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>7.417779542189435</v>
+        <v>7.41778</v>
       </c>
     </row>
     <row r="425">
@@ -13159,7 +13622,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>84.21216208741049</v>
+        <v>84.21216200000001</v>
       </c>
     </row>
     <row r="426">
@@ -13177,7 +13640,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>50.36584401521459</v>
+        <v>50.365844</v>
       </c>
     </row>
     <row r="427">
@@ -13195,7 +13658,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>8.969279928117066</v>
+        <v>8.969279999999999</v>
       </c>
     </row>
     <row r="428">
@@ -13213,7 +13676,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>84.73964866659612</v>
+        <v>84.739649</v>
       </c>
     </row>
     <row r="429">
@@ -13231,7 +13694,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>48.02596045028307</v>
+        <v>48.02596</v>
       </c>
     </row>
     <row r="430">
@@ -13249,7 +13712,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>8.452021518178032</v>
+        <v>8.452021999999999</v>
       </c>
     </row>
     <row r="431">
@@ -13267,7 +13730,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>110.2112718674485</v>
+        <v>110.211272</v>
       </c>
     </row>
     <row r="432">
@@ -13285,7 +13748,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>64.86841583860632</v>
+        <v>64.868416</v>
       </c>
     </row>
     <row r="433">
@@ -13303,7 +13766,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>7.789989558163865</v>
+        <v>7.78999</v>
       </c>
     </row>
     <row r="434">
@@ -13321,7 +13784,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>97.25028643789403</v>
+        <v>97.250286</v>
       </c>
     </row>
     <row r="435">
@@ -13339,7 +13802,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>58.61318962925962</v>
+        <v>58.61319</v>
       </c>
     </row>
     <row r="436">
@@ -13357,7 +13820,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>9.108050133169341</v>
+        <v>9.10805</v>
       </c>
     </row>
     <row r="437">
@@ -13375,7 +13838,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>122.6406722419367</v>
+        <v>122.640672</v>
       </c>
     </row>
     <row r="438">
@@ -13393,7 +13856,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>48.48166181222052</v>
+        <v>48.481662</v>
       </c>
     </row>
     <row r="439">
@@ -13411,7 +13874,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>7.504017315723195</v>
+        <v>7.504017</v>
       </c>
     </row>
     <row r="440">
@@ -13429,7 +13892,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>86.65203899050141</v>
+        <v>86.652039</v>
       </c>
     </row>
     <row r="441">
@@ -13447,7 +13910,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>65.47887525981091</v>
+        <v>65.478875</v>
       </c>
     </row>
     <row r="442">
@@ -13465,7 +13928,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>6.501095792676019</v>
+        <v>6.501096</v>
       </c>
     </row>
     <row r="443">
@@ -13483,7 +13946,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>100.2101904209748</v>
+        <v>100.21019</v>
       </c>
     </row>
     <row r="444">
@@ -13501,7 +13964,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>57.34295692418527</v>
+        <v>57.342957</v>
       </c>
     </row>
     <row r="445">
@@ -13519,7 +13982,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>7.883978736841018</v>
+        <v>7.883979</v>
       </c>
     </row>
     <row r="446">
@@ -13537,7 +14000,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>95.79304277965804</v>
+        <v>95.793043</v>
       </c>
     </row>
     <row r="447">
@@ -13555,7 +14018,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>59.15075818326355</v>
+        <v>59.150758</v>
       </c>
     </row>
     <row r="448">
@@ -13573,7 +14036,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>7.795669334101857</v>
+        <v>7.795669</v>
       </c>
     </row>
     <row r="449">
@@ -13591,7 +14054,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>93.39788189162962</v>
+        <v>93.397882</v>
       </c>
     </row>
     <row r="450">
@@ -13609,7 +14072,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>67.44052026572707</v>
+        <v>67.44052000000001</v>
       </c>
     </row>
     <row r="451">
@@ -13627,7 +14090,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>6.38203864508034</v>
+        <v>6.382039</v>
       </c>
     </row>
     <row r="452">
@@ -13645,7 +14108,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>94.01563617626159</v>
+        <v>94.015636</v>
       </c>
     </row>
     <row r="453">
@@ -13663,7 +14126,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>52.56005320081496</v>
+        <v>52.560053</v>
       </c>
     </row>
     <row r="454">
@@ -13681,7 +14144,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>7.560074439673128</v>
+        <v>7.560074</v>
       </c>
     </row>
     <row r="455">
@@ -13699,7 +14162,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>108.964405434799</v>
+        <v>108.964405</v>
       </c>
     </row>
     <row r="456">
@@ -13717,7 +14180,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>64.32355407915675</v>
+        <v>64.323554</v>
       </c>
     </row>
     <row r="457">
@@ -13735,7 +14198,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>9.374028370244883</v>
+        <v>9.374027999999999</v>
       </c>
     </row>
     <row r="458">
@@ -13753,7 +14216,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>83.69112192214936</v>
+        <v>83.69112199999999</v>
       </c>
     </row>
     <row r="459">
@@ -13771,7 +14234,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>52.42993465123005</v>
+        <v>52.429935</v>
       </c>
     </row>
     <row r="460">
@@ -13789,7 +14252,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>9.101167217558235</v>
+        <v>9.101167</v>
       </c>
     </row>
     <row r="461">
@@ -13807,7 +14270,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>98.22411492931772</v>
+        <v>98.224115</v>
       </c>
     </row>
     <row r="462">
@@ -13825,7 +14288,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>73.18946323343231</v>
+        <v>73.189463</v>
       </c>
     </row>
     <row r="463">
@@ -13843,7 +14306,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>8.031191236980879</v>
+        <v>8.031191</v>
       </c>
     </row>
     <row r="464">
@@ -13861,7 +14324,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>83.77039413352607</v>
+        <v>83.770394</v>
       </c>
     </row>
     <row r="465">
@@ -13879,7 +14342,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>60.122571128628</v>
+        <v>60.122571</v>
       </c>
     </row>
     <row r="466">
@@ -13897,7 +14360,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>8.428415198441922</v>
+        <v>8.428414999999999</v>
       </c>
     </row>
     <row r="467">
@@ -13915,7 +14378,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>88.12269580154124</v>
+        <v>88.122696</v>
       </c>
     </row>
     <row r="468">
@@ -13933,7 +14396,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>65.22019512858292</v>
+        <v>65.220195</v>
       </c>
     </row>
     <row r="469">
@@ -13951,7 +14414,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>8.003978512528954</v>
+        <v>8.003978999999999</v>
       </c>
     </row>
     <row r="470">
@@ -13969,7 +14432,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>85.24829770826963</v>
+        <v>85.24829800000001</v>
       </c>
     </row>
     <row r="471">
@@ -13987,7 +14450,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>59.49381401827559</v>
+        <v>59.493814</v>
       </c>
     </row>
     <row r="472">
@@ -14005,7 +14468,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>8.252096745594535</v>
+        <v>8.252096999999999</v>
       </c>
     </row>
     <row r="473">
@@ -14023,7 +14486,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>99.33302976075265</v>
+        <v>99.33302999999999</v>
       </c>
     </row>
     <row r="474">
@@ -14041,7 +14504,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>47.09701916222419</v>
+        <v>47.097019</v>
       </c>
     </row>
     <row r="475">
@@ -14059,7 +14522,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>8.360106793244983</v>
+        <v>8.360106999999999</v>
       </c>
     </row>
     <row r="476">
@@ -14077,7 +14540,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>110.4952386177405</v>
+        <v>110.495239</v>
       </c>
     </row>
     <row r="477">
@@ -14095,7 +14558,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>72.98683546244332</v>
+        <v>72.986835</v>
       </c>
     </row>
     <row r="478">
@@ -14113,7 +14576,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>7.779602678770477</v>
+        <v>7.779603</v>
       </c>
     </row>
     <row r="479">
@@ -14131,7 +14594,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>88.08238272972788</v>
+        <v>88.08238299999999</v>
       </c>
     </row>
     <row r="480">
@@ -14149,7 +14612,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>64.05738475023647</v>
+        <v>64.057385</v>
       </c>
     </row>
     <row r="481">
@@ -14167,7 +14630,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>9.114335015576838</v>
+        <v>9.114335000000001</v>
       </c>
     </row>
     <row r="482">
@@ -14185,7 +14648,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>111.5741725886235</v>
+        <v>111.574173</v>
       </c>
     </row>
     <row r="483">
@@ -14203,7 +14666,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>63.73578808787661</v>
+        <v>63.735788</v>
       </c>
     </row>
     <row r="484">
@@ -14221,7 +14684,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>9.098963761459643</v>
+        <v>9.098964</v>
       </c>
     </row>
     <row r="485">
@@ -14239,7 +14702,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>105.0448999299361</v>
+        <v>105.0449</v>
       </c>
     </row>
     <row r="486">
@@ -14257,7 +14720,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>47.91232109945599</v>
+        <v>47.912321</v>
       </c>
     </row>
     <row r="487">
@@ -14275,7 +14738,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>7.814213103324402</v>
+        <v>7.814213</v>
       </c>
     </row>
     <row r="488">
@@ -14293,7 +14756,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>93.30298173222546</v>
+        <v>93.302982</v>
       </c>
     </row>
     <row r="489">
@@ -14311,7 +14774,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>58.07609930712594</v>
+        <v>58.076099</v>
       </c>
     </row>
     <row r="490">
@@ -14329,7 +14792,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>8.31997480051861</v>
+        <v>8.319974999999999</v>
       </c>
     </row>
     <row r="491">
@@ -14347,7 +14810,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>85.95678477704304</v>
+        <v>85.956785</v>
       </c>
     </row>
     <row r="492">
@@ -14365,7 +14828,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>65.72802191052844</v>
+        <v>65.728022</v>
       </c>
     </row>
     <row r="493">
@@ -14383,7 +14846,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>6.693857415664498</v>
+        <v>6.693857</v>
       </c>
     </row>
     <row r="494">
@@ -14401,7 +14864,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>118.8536777559593</v>
+        <v>118.853678</v>
       </c>
     </row>
     <row r="495">
@@ -14419,7 +14882,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>53.47480398269799</v>
+        <v>53.474804</v>
       </c>
     </row>
     <row r="496">
@@ -14437,7 +14900,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>8.385426657380814</v>
+        <v>8.385427</v>
       </c>
     </row>
     <row r="497">
@@ -14455,7 +14918,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>79.15333044229824</v>
+        <v>79.15333</v>
       </c>
     </row>
     <row r="498">
@@ -14473,7 +14936,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>49.71249184545857</v>
+        <v>49.712492</v>
       </c>
     </row>
     <row r="499">
@@ -14491,7 +14954,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>9.974923417077022</v>
+        <v>9.974923</v>
       </c>
     </row>
     <row r="500">
@@ -14509,7 +14972,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>97.75714620475992</v>
+        <v>97.75714600000001</v>
       </c>
     </row>
     <row r="501">
@@ -14527,7 +14990,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>58.5604310518712</v>
+        <v>58.560431</v>
       </c>
     </row>
     <row r="502">
@@ -14545,7 +15008,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>7.457697110670161</v>
+        <v>7.457697</v>
       </c>
     </row>
     <row r="503">
@@ -14563,7 +15026,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>109.0564839516554</v>
+        <v>109.056484</v>
       </c>
     </row>
     <row r="504">
@@ -14581,7 +15044,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>73.5976828860598</v>
+        <v>73.597683</v>
       </c>
     </row>
     <row r="505">
@@ -14599,7 +15062,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>7.662271034003592</v>
+        <v>7.662271</v>
       </c>
     </row>
     <row r="506">
@@ -14617,7 +15080,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>105.4093168379028</v>
+        <v>105.409317</v>
       </c>
     </row>
     <row r="507">
@@ -14635,7 +15098,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>68.09425456574412</v>
+        <v>68.094255</v>
       </c>
     </row>
     <row r="508">
@@ -14653,7 +15116,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>6.905718956493824</v>
+        <v>6.905719</v>
       </c>
     </row>
     <row r="509">
@@ -14671,7 +15134,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>87.58847641382258</v>
+        <v>87.588476</v>
       </c>
     </row>
     <row r="510">
@@ -14689,7 +15152,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>56.26076679329</v>
+        <v>56.260767</v>
       </c>
     </row>
     <row r="511">
@@ -14707,7 +15170,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6.866064861562951</v>
+        <v>6.866065</v>
       </c>
     </row>
     <row r="512">
@@ -14725,7 +15188,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>122.8466386377199</v>
+        <v>122.846639</v>
       </c>
     </row>
     <row r="513">
@@ -14743,7 +15206,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>45.96122885338482</v>
+        <v>45.961229</v>
       </c>
     </row>
     <row r="514">
@@ -14761,7 +15224,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>7.192682024837723</v>
+        <v>7.192682</v>
       </c>
     </row>
     <row r="515">
@@ -14779,7 +15242,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>115.0258418806951</v>
+        <v>115.025842</v>
       </c>
     </row>
     <row r="516">
@@ -14797,7 +15260,7 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>48.29057897932822</v>
+        <v>48.290579</v>
       </c>
     </row>
     <row r="517">
@@ -14815,7 +15278,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>7.100912856488194</v>
+        <v>7.100913</v>
       </c>
     </row>
     <row r="518">
@@ -14833,7 +15296,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>117.9594163799201</v>
+        <v>117.959416</v>
       </c>
     </row>
     <row r="519">
@@ -14851,7 +15314,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>66.76611433598973</v>
+        <v>66.766114</v>
       </c>
     </row>
     <row r="520">
@@ -14869,7 +15332,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>9.020104606873137</v>
+        <v>9.020104999999999</v>
       </c>
     </row>
     <row r="521">
@@ -14887,7 +15350,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>110.4135760684724</v>
+        <v>110.413576</v>
       </c>
     </row>
     <row r="522">
@@ -14905,7 +15368,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>70.66774850615431</v>
+        <v>70.667749</v>
       </c>
     </row>
     <row r="523">
@@ -14923,7 +15386,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>8.747056267491493</v>
+        <v>8.747056000000001</v>
       </c>
     </row>
     <row r="524">
@@ -14941,7 +15404,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>94.05914093590981</v>
+        <v>94.059141</v>
       </c>
     </row>
     <row r="525">
@@ -14959,7 +15422,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>69.74883454963226</v>
+        <v>69.748835</v>
       </c>
     </row>
     <row r="526">
@@ -14977,7 +15440,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>7.979892641780226</v>
+        <v>7.979893</v>
       </c>
     </row>
     <row r="527">
@@ -14995,7 +15458,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>101.5148805894678</v>
+        <v>101.514881</v>
       </c>
     </row>
     <row r="528">
@@ -15013,7 +15476,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>59.58966251171789</v>
+        <v>59.589663</v>
       </c>
     </row>
     <row r="529">
@@ -15031,7 +15494,7 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>8.393429726849865</v>
+        <v>8.39343</v>
       </c>
     </row>
     <row r="530">
@@ -15049,7 +15512,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>117.028534297631</v>
+        <v>117.028534</v>
       </c>
     </row>
     <row r="531">
@@ -15067,7 +15530,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>51.33698422799583</v>
+        <v>51.336984</v>
       </c>
     </row>
     <row r="532">
@@ -15085,7 +15548,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>8.023007234540991</v>
+        <v>8.023007</v>
       </c>
     </row>
     <row r="533">
@@ -15103,7 +15566,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>107.5603079690621</v>
+        <v>107.560308</v>
       </c>
     </row>
     <row r="534">
@@ -15121,7 +15584,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>60.94155878725011</v>
+        <v>60.941559</v>
       </c>
     </row>
     <row r="535">
@@ -15139,7 +15602,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>7.530907203829993</v>
+        <v>7.530907</v>
       </c>
     </row>
     <row r="536">
@@ -15157,7 +15620,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>104.357496062461</v>
+        <v>104.357496</v>
       </c>
     </row>
     <row r="537">
@@ -15175,7 +15638,7 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>56.8790320307882</v>
+        <v>56.879032</v>
       </c>
     </row>
     <row r="538">
@@ -15193,7 +15656,7 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>6.888148551915012</v>
+        <v>6.888149</v>
       </c>
     </row>
     <row r="539">
@@ -15211,7 +15674,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>90.42822401530807</v>
+        <v>90.428224</v>
       </c>
     </row>
     <row r="540">
@@ -15229,7 +15692,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>56.63638569843668</v>
+        <v>56.636386</v>
       </c>
     </row>
     <row r="541">
@@ -15247,7 +15710,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>3.904744600658807</v>
+        <v>3.904745</v>
       </c>
     </row>
     <row r="542">
@@ -15265,7 +15728,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>89.15879884179431</v>
+        <v>89.158799</v>
       </c>
     </row>
     <row r="543">
@@ -15283,7 +15746,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>72.88962027094547</v>
+        <v>72.88961999999999</v>
       </c>
     </row>
     <row r="544">
@@ -15301,7 +15764,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>8.532420198814297</v>
+        <v>8.53242</v>
       </c>
     </row>
     <row r="545">
@@ -15319,7 +15782,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>113.2156949311487</v>
+        <v>113.215695</v>
       </c>
     </row>
     <row r="546">
@@ -15337,7 +15800,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>49.1523153891703</v>
+        <v>49.152315</v>
       </c>
     </row>
     <row r="547">
@@ -15355,7 +15818,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>8.716512478056179</v>
+        <v>8.716512</v>
       </c>
     </row>
     <row r="548">
@@ -15373,7 +15836,7 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>109.5576709574224</v>
+        <v>109.557671</v>
       </c>
     </row>
     <row r="549">
@@ -15391,7 +15854,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>64.86911035744012</v>
+        <v>64.86911000000001</v>
       </c>
     </row>
     <row r="550">
@@ -15409,7 +15872,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>8.067738011887203</v>
+        <v>8.067738</v>
       </c>
     </row>
     <row r="551">
@@ -15427,7 +15890,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>98.38373499256325</v>
+        <v>98.383735</v>
       </c>
     </row>
     <row r="552">
@@ -15445,7 +15908,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>70.84901512521552</v>
+        <v>70.84901499999999</v>
       </c>
     </row>
     <row r="553">
@@ -15463,7 +15926,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>6.363565875688725</v>
+        <v>6.363566</v>
       </c>
     </row>
   </sheetData>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1864,6 +1864,106 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>REACTIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E-13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>183</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" t="n">
+        <v>400</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_PLANTA</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
         </is>
       </c>
     </row>
@@ -3326,19 +3426,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3901,7 +4001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3999,7 +4099,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4008,13 +4108,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4023,13 +4123,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4038,13 +4138,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4053,13 +4153,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4068,28 +4168,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4098,13 +4198,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4113,13 +4213,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4128,21 +4228,51 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>BOREAS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>DODERO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C18" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4576,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4604,7 +4734,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4618,13 +4748,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4638,13 +4768,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4658,13 +4788,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4678,13 +4808,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4698,13 +4828,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4718,13 +4848,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4738,13 +4868,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4758,13 +4888,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4778,13 +4908,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4798,13 +4928,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4818,13 +4948,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4838,13 +4968,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4858,13 +4988,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4878,13 +5008,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4898,18 +5028,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4918,18 +5048,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4938,18 +5068,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4958,13 +5088,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4978,13 +5108,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4998,13 +5128,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5018,13 +5148,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5038,13 +5168,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5058,13 +5188,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5078,13 +5208,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5098,13 +5228,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5118,13 +5248,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5138,13 +5268,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5158,13 +5288,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5178,26 +5308,146 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>BOREAS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RUTA9</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>DODERO</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DODERO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5212,7 +5462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5240,7 +5490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5260,17 +5510,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5280,12 +5530,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRINOA</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5294,7 +5544,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -5305,16 +5555,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -5325,16 +5575,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -5345,76 +5595,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORRY</t>
+          <t>FRINOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -5425,16 +5675,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -5445,16 +5695,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -5465,76 +5715,76 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BOREAS</t>
+          <t>NORRY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -5545,16 +5795,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -5565,16 +5815,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -5585,76 +5835,76 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RUTA9</t>
+          <t>BOREAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -5665,16 +5915,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5685,16 +5935,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -5705,76 +5955,76 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DODERO</t>
+          <t>RUTA9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -5785,16 +6035,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -5805,16 +6055,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>JUGO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -5825,47 +6075,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ACEITE</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CROSS_DOCK</t>
+          <t>CONSOLIDACION</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUGO</t>
+          <t>CASCARA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASCARA</t>
+          <t>ACEITE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5874,13 +6124,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DODERO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5890,17 +6140,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CONSOLIDACION</t>
+          <t>CROSS_DOCK</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5914,13 +6164,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5934,26 +6184,86 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>ZARATE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ACEITE</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JUGO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>CONSOLIDACION</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CASCARA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ACEITE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>16</v>
       </c>
     </row>

--- a/datos/entrada_ejemplo.xlsx
+++ b/datos/entrada_ejemplo.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,6 +567,51 @@
           <t>politica_frio_propio</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>politica_seleccion</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>servicio_minimo_proyectado</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>factor_tarifa_flete</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>factor_tarifa_round_trip</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>factor_tarifa_cross_dock</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>factor_tarifa_terminal</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>factor_consolidacion_planta</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>factor_cupo_cross_dock</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>factor_capacidad_terminal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -667,6 +712,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -767,6 +841,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -867,6 +970,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -967,6 +1099,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1067,6 +1228,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1167,6 +1357,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1267,6 +1486,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1367,6 +1615,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1467,6 +1744,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1567,6 +1873,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1667,6 +2002,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1767,6 +2131,35 @@
           <t>FLEXIBLE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_TERMINAL</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1867,6 +2260,35 @@
           <t>REACTIVA</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1966,6 +2388,2873 @@
         <is>
           <t>FLEXIBLE</t>
         </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>FIJA_PLANTA</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>E-14</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>183</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" t="n">
+        <v>400</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>70</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>MENOR_COSTO_INCREMENTAL_FACTIBLE</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>183</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" t="n">
+        <v>400</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>70</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>MENOR_COSTO_END_TO_END_FACTIBLE</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E-16</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>183</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>400</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>70</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>PRIORIDAD_FRIO_PROPIO</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E-17</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>183</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>400</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>70</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>MENOR_COSTO_INCREMENTAL_FACTIBLE</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E-18</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>183</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" t="n">
+        <v>400</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>70</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E-19</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>183</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="n">
+        <v>400</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>70</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E-20</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>183</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>400</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>70</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>E-21</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>183</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G23" t="n">
+        <v>400</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" t="n">
+        <v>70</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E-22</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>183</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40</v>
+      </c>
+      <c r="G24" t="n">
+        <v>400</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>25</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E-23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>183</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" t="n">
+        <v>400</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>25</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E-24</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>183</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" t="n">
+        <v>400</v>
+      </c>
+      <c r="H26" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>70</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E-25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>183</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" t="n">
+        <v>400</v>
+      </c>
+      <c r="H27" t="n">
+        <v>15</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E-26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>183</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" t="n">
+        <v>400</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>70</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E-27</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>183</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" t="n">
+        <v>400</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" t="n">
+        <v>70</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E-28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>183</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" t="n">
+        <v>400</v>
+      </c>
+      <c r="H30" t="n">
+        <v>60</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>70</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E-32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>183</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="n">
+        <v>400</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>70</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>E-33</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>183</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" t="n">
+        <v>400</v>
+      </c>
+      <c r="H32" t="n">
+        <v>45</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>25</v>
+      </c>
+      <c r="L32" t="n">
+        <v>70</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E-29</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>183</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40</v>
+      </c>
+      <c r="G33" t="n">
+        <v>400</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>25</v>
+      </c>
+      <c r="L33" t="n">
+        <v>70</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E-30</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>183</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40</v>
+      </c>
+      <c r="G34" t="n">
+        <v>400</v>
+      </c>
+      <c r="H34" t="n">
+        <v>15</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>25</v>
+      </c>
+      <c r="L34" t="n">
+        <v>70</v>
+      </c>
+      <c r="M34" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>FIJA_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>E-31</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>183</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>40</v>
+      </c>
+      <c r="G35" t="n">
+        <v>400</v>
+      </c>
+      <c r="H35" t="n">
+        <v>15</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>70</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_PLANTA</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>FIJA_PLANTA</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>E-34</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>183</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>40</v>
+      </c>
+      <c r="G36" t="n">
+        <v>400</v>
+      </c>
+      <c r="H36" t="n">
+        <v>15</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>70</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_DEPOSITO</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E-35</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>183</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>40</v>
+      </c>
+      <c r="G37" t="n">
+        <v>400</v>
+      </c>
+      <c r="H37" t="n">
+        <v>15</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>25</v>
+      </c>
+      <c r="L37" t="n">
+        <v>70</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>CONSOLIDACION_TERMINAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>ESTANDAR</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>105</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>FLEXIBLE</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>FIJA_CROSS_DOCK_TERMINAL</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
